--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1313-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1313-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2E5B2CD-62BD-402A-B707-1B8487C6CC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A55A0A9-F3CB-44D4-B4A0-0C99B2805477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{5D1C78BF-4A7E-4DC6-802A-D64976308B59}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{CFB25E14-40C4-43D8-83C2-54F99D11B7CB}"/>
   </bookViews>
   <sheets>
     <sheet name="1313-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1586,29 +1586,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{208439A5-75FE-47E2-8FA7-C5A6E748193A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B7382A5-ED07-443F-AE32-E4E58C9030AA}">
   <dimension ref="A1:X49"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1642,7 +1641,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1678,7 +1677,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1730,7 +1729,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1798,7 +1797,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2024</v>
       </c>
@@ -1870,7 +1869,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="41">
         <v>2023</v>
       </c>
@@ -1942,7 +1941,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="39">
         <v>2022</v>
       </c>
@@ -2014,7 +2013,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="41">
         <v>2021</v>
       </c>
@@ -2086,7 +2085,7 @@
         <v>8.58</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <v>2020</v>
       </c>
@@ -2158,7 +2157,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="41">
         <v>2019</v>
       </c>
@@ -2230,7 +2229,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="43">
         <v>2018</v>
       </c>
@@ -2302,7 +2301,7 @@
         <v>5.05</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="45"/>
       <c r="B12" s="46"/>
       <c r="C12" s="18" t="s">
@@ -2330,7 +2329,7 @@
       <c r="W12" s="52"/>
       <c r="X12" s="48"/>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="41">
         <v>2017</v>
       </c>
@@ -2402,7 +2401,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2016</v>
       </c>
@@ -2474,7 +2473,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="41">
         <v>2015</v>
       </c>
@@ -2546,7 +2545,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2014</v>
       </c>
@@ -2618,7 +2617,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="41">
         <v>2013</v>
       </c>
@@ -2690,7 +2689,7 @@
         <v>4.04</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2012</v>
       </c>
@@ -2762,7 +2761,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="41">
         <v>2011</v>
       </c>
@@ -2834,7 +2833,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2010</v>
       </c>
@@ -2906,7 +2905,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="41">
         <v>2009</v>
       </c>
@@ -2978,7 +2977,7 @@
         <v>7.11</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2008</v>
       </c>
@@ -3050,7 +3049,7 @@
         <v>2.2599999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="41">
         <v>2007</v>
       </c>
@@ -3122,7 +3121,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2006</v>
       </c>
@@ -3194,7 +3193,7 @@
         <v>7.79</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="41">
         <v>2005</v>
       </c>
@@ -3266,7 +3265,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2004</v>
       </c>
@@ -3338,7 +3337,7 @@
         <v>8.61</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="41">
         <v>2003</v>
       </c>
@@ -3410,7 +3409,7 @@
         <v>4.04</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>2002</v>
       </c>
@@ -3482,7 +3481,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="41">
         <v>2001</v>
       </c>
@@ -3554,7 +3553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>2000</v>
       </c>
@@ -3626,7 +3625,7 @@
         <v>9.3800000000000008</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="41">
         <v>1999</v>
       </c>
@@ -3698,7 +3697,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>1998</v>
       </c>
@@ -3770,7 +3769,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="41">
         <v>1997</v>
       </c>
@@ -3842,7 +3841,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>1996</v>
       </c>
@@ -3914,7 +3913,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="41">
         <v>1995</v>
       </c>
@@ -3986,7 +3985,7 @@
         <v>7.46</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="43">
         <v>1994</v>
       </c>
@@ -4058,7 +4057,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="45"/>
       <c r="B37" s="46"/>
       <c r="C37" s="18" t="s">
@@ -4086,7 +4085,7 @@
       <c r="W37" s="52"/>
       <c r="X37" s="48"/>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="41">
         <v>1993</v>
       </c>
@@ -4158,7 +4157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="39">
         <v>1992</v>
       </c>
@@ -4230,7 +4229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="53">
         <v>1991</v>
       </c>
@@ -4302,7 +4301,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="55"/>
       <c r="B41" s="56"/>
       <c r="C41" s="22" t="s">
@@ -4330,7 +4329,7 @@
       <c r="W41" s="62"/>
       <c r="X41" s="58"/>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="39">
         <v>1990</v>
       </c>
@@ -4402,7 +4401,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="41">
         <v>1989</v>
       </c>
@@ -4474,7 +4473,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="39">
         <v>1988</v>
       </c>
@@ -4546,7 +4545,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="41">
         <v>1987</v>
       </c>
@@ -4618,7 +4617,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="39">
         <v>1986</v>
       </c>
@@ -4690,7 +4689,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="41">
         <v>1985</v>
       </c>
@@ -4762,7 +4761,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="39">
         <v>1984</v>
       </c>
@@ -4834,7 +4833,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="41" t="s">
         <v>62</v>
       </c>
